--- a/tiflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Bundle-OP-Accept.xlsx
+++ b/tiflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Bundle-OP-Accept.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4092" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4072" uniqueCount="349">
   <si>
     <t>Property</t>
   </si>
@@ -268,8 +268,8 @@
     <t>A container for a collection of resources.</t>
   </si>
   <si>
-    <t>bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}
-bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}</t>
+    <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
+bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -384,16 +384,6 @@
   </si>
   <si>
     <t>Persistent identity generally only matters for batches of type Document, Message, and Collection. It would not normally be populated for search and history results and servers ignore Bundle.identifier when processing batches and transactions. For Documents  the .identifier SHALL be populated such that the .identifier is globally unique.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
-  </si>
-  <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>ClinicalDocument.id</t>
@@ -496,9 +486,6 @@
 This specification defines some specific uses of Bundle.link for [searching](http://hl7.org/fhir/R4/search.html#conformance) and [paging](http://hl7.org/fhir/R4/http.html#paging), but no specific uses for Bundle.entry.link, and no defined function in a transaction - the meaning is implementation specific.</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Bundle.link.id</t>
   </si>
   <si>
@@ -515,6 +502,9 @@
     <t>Element.id</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Bundle.link.extension</t>
   </si>
   <si>
@@ -535,16 +525,6 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -581,9 +561,6 @@
     <t>A name which details the functional use for this link - see [http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1](http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1).</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Bundle.link.url</t>
   </si>
   <si>
@@ -591,9 +568,6 @@
   </si>
   <si>
     <t>The reference details for the link.</t>
-  </si>
-  <si>
-    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Bundle.entry</t>
@@ -618,8 +592,8 @@
     <t>closed</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}</t>
+    <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
+bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>Bundle.entry.id</t>
@@ -668,9 +642,6 @@
     <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
   </si>
   <si>
-    <t>Entity. Role, or Act</t>
-  </si>
-  <si>
     <t>Bundle.entry.search</t>
   </si>
   <si>
@@ -680,8 +651,8 @@
     <t>Information about the search process that lead to the creation of this entry.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-2</t>
+    <t xml:space="preserve">bdl-2
+</t>
   </si>
   <si>
     <t>Bundle.entry.search.id</t>
@@ -737,8 +708,8 @@
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-3</t>
+    <t xml:space="preserve">bdl-3
+</t>
   </si>
   <si>
     <t>Bundle.entry.request.id</t>
@@ -792,9 +763,6 @@
     <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
   </si>
   <si>
-    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
-  </si>
-  <si>
     <t>Bundle.entry.request.ifMatch</t>
   </si>
   <si>
@@ -822,8 +790,8 @@
     <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-4</t>
+    <t xml:space="preserve">bdl-4
+</t>
   </si>
   <si>
     <t>Bundle.entry.response.id</t>
@@ -1473,15 +1441,15 @@
     <col min="26" max="26" width="42.01953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.91015625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.98828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="53.91015625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="123.23828125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="22.78515625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.84375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -2270,30 +2238,30 @@
         <v>88</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2319,13 +2287,13 @@
         <v>108</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2333,32 +2301,32 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="Z8" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="S8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>133</v>
-      </c>
       <c r="AA8" t="s" s="2">
         <v>78</v>
       </c>
@@ -2375,7 +2343,7 @@
         <v>78</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>88</v>
@@ -2399,15 +2367,15 @@
         <v>78</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2430,16 +2398,16 @@
         <v>89</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="N9" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2489,7 +2457,7 @@
         <v>78</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -2510,18 +2478,18 @@
         <v>78</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2544,16 +2512,16 @@
         <v>89</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="N10" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="L10" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2603,7 +2571,7 @@
         <v>78</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2612,7 +2580,7 @@
         <v>88</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>100</v>
@@ -2632,10 +2600,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2658,16 +2626,16 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="N11" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2717,7 +2685,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2726,7 +2694,7 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>100</v>
@@ -2735,7 +2703,7 @@
         <v>78</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>78</v>
@@ -2746,10 +2714,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2772,13 +2740,13 @@
         <v>78</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2829,7 +2797,7 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -2847,7 +2815,7 @@
         <v>78</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>78</v>
@@ -2858,14 +2826,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2884,16 +2852,16 @@
         <v>78</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2931,19 +2899,19 @@
         <v>78</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -2955,13 +2923,13 @@
         <v>78</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>78</v>
@@ -2972,14 +2940,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2998,19 +2966,19 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L14" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O14" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>78</v>
@@ -3059,7 +3027,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3071,7 +3039,7 @@
         <v>78</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>78</v>
@@ -3088,10 +3056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3114,17 +3082,15 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>78</v>
@@ -3173,7 +3139,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>88</v>
@@ -3202,10 +3168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3231,14 +3197,12 @@
         <v>102</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>78</v>
@@ -3287,7 +3251,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>88</v>
@@ -3316,10 +3280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3327,10 +3291,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>78</v>
@@ -3342,13 +3306,13 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3387,19 +3351,19 @@
         <v>78</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3408,16 +3372,16 @@
         <v>80</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>78</v>
@@ -3428,10 +3392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3454,13 +3418,13 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3511,7 +3475,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3529,7 +3493,7 @@
         <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -3540,14 +3504,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3566,16 +3530,16 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3613,19 +3577,19 @@
         <v>78</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3637,13 +3601,13 @@
         <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>78</v>
@@ -3654,14 +3618,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3680,19 +3644,19 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O20" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -3741,7 +3705,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3753,7 +3717,7 @@
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
@@ -3770,10 +3734,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3799,10 +3763,10 @@
         <v>78</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3853,7 +3817,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3865,7 +3829,7 @@
         <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>78</v>
@@ -3882,10 +3846,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3911,13 +3875,13 @@
         <v>102</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3967,7 +3931,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3996,10 +3960,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4022,13 +3986,13 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4079,7 +4043,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4097,7 +4061,7 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
@@ -4108,10 +4072,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4134,13 +4098,13 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4191,7 +4155,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4200,7 +4164,7 @@
         <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>100</v>
@@ -4209,7 +4173,7 @@
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -4220,10 +4184,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4246,13 +4210,13 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4303,7 +4267,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4321,7 +4285,7 @@
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -4332,14 +4296,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4358,16 +4322,16 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4405,19 +4369,19 @@
         <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4429,13 +4393,13 @@
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4446,14 +4410,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4472,19 +4436,19 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O27" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4533,7 +4497,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4545,7 +4509,7 @@
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
@@ -4562,10 +4526,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4591,13 +4555,13 @@
         <v>108</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4623,13 +4587,13 @@
         <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>78</v>
@@ -4647,7 +4611,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4676,10 +4640,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4702,16 +4666,16 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4761,7 +4725,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4790,10 +4754,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4816,13 +4780,13 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4873,7 +4837,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4882,7 +4846,7 @@
         <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>100</v>
@@ -4891,7 +4855,7 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -4902,10 +4866,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4928,13 +4892,13 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4985,7 +4949,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5003,7 +4967,7 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -5014,14 +4978,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5040,16 +5004,16 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5087,19 +5051,19 @@
         <v>78</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5111,13 +5075,13 @@
         <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -5128,14 +5092,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5154,19 +5118,19 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O33" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5215,7 +5179,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5227,7 +5191,7 @@
         <v>78</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>78</v>
@@ -5244,10 +5208,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5273,10 +5237,10 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5303,13 +5267,13 @@
         <v>78</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>78</v>
@@ -5327,7 +5291,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>88</v>
@@ -5356,10 +5320,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5385,13 +5349,13 @@
         <v>102</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5441,7 +5405,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>88</v>
@@ -5470,10 +5434,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5496,17 +5460,15 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -5555,7 +5517,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5584,10 +5546,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5610,17 +5572,15 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -5669,7 +5629,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5698,10 +5658,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5724,17 +5684,15 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -5783,7 +5741,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5812,10 +5770,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5838,17 +5796,15 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -5897,7 +5853,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -5926,10 +5882,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5952,13 +5908,13 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6009,7 +5965,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6018,7 +5974,7 @@
         <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>100</v>
@@ -6027,7 +5983,7 @@
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6038,10 +5994,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6064,13 +6020,13 @@
         <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6121,7 +6077,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6139,7 +6095,7 @@
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -6150,14 +6106,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6176,16 +6132,16 @@
         <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6223,19 +6179,19 @@
         <v>78</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6247,13 +6203,13 @@
         <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -6264,14 +6220,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6290,19 +6246,19 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L43" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O43" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6351,7 +6307,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6363,7 +6319,7 @@
         <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>78</v>
@@ -6380,10 +6336,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6406,17 +6362,15 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -6465,7 +6419,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>88</v>
@@ -6494,10 +6448,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6523,14 +6477,12 @@
         <v>102</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -6579,7 +6531,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6608,10 +6560,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6634,16 +6586,16 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6693,7 +6645,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6722,10 +6674,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6748,16 +6700,16 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6807,7 +6759,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -6836,10 +6788,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6862,16 +6814,16 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6921,7 +6873,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -6939,7 +6891,7 @@
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -6950,13 +6902,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>78</v>
@@ -6978,13 +6930,13 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7035,7 +6987,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7044,16 +6996,16 @@
         <v>80</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7064,10 +7016,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7090,13 +7042,13 @@
         <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7147,7 +7099,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7165,7 +7117,7 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
@@ -7176,14 +7128,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7202,16 +7154,16 @@
         <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7249,19 +7201,19 @@
         <v>78</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7273,13 +7225,13 @@
         <v>78</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>78</v>
@@ -7290,14 +7242,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7316,19 +7268,19 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L52" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O52" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -7377,7 +7329,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7389,7 +7341,7 @@
         <v>78</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>78</v>
@@ -7406,10 +7358,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7435,10 +7387,10 @@
         <v>81</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7489,7 +7441,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7501,7 +7453,7 @@
         <v>78</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>78</v>
@@ -7518,10 +7470,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7547,13 +7499,13 @@
         <v>102</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7603,7 +7555,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7632,10 +7584,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7658,13 +7610,13 @@
         <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7715,7 +7667,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7733,7 +7685,7 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -7744,10 +7696,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7770,13 +7722,13 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7827,7 +7779,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -7836,7 +7788,7 @@
         <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>100</v>
@@ -7845,7 +7797,7 @@
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -7856,10 +7808,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7882,13 +7834,13 @@
         <v>78</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7939,7 +7891,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -7957,7 +7909,7 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -7968,14 +7920,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7994,16 +7946,16 @@
         <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8041,19 +7993,19 @@
         <v>78</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8065,13 +8017,13 @@
         <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -8082,14 +8034,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8108,19 +8060,19 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L59" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O59" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8169,7 +8121,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8181,7 +8133,7 @@
         <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>78</v>
@@ -8198,10 +8150,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8227,13 +8179,13 @@
         <v>108</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8259,13 +8211,13 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -8283,7 +8235,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8312,10 +8264,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8338,16 +8290,16 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8397,7 +8349,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8426,10 +8378,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8452,13 +8404,13 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8509,7 +8461,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8518,7 +8470,7 @@
         <v>88</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>100</v>
@@ -8527,7 +8479,7 @@
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -8538,10 +8490,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8564,13 +8516,13 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8621,7 +8573,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -8639,7 +8591,7 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -8650,14 +8602,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8676,16 +8628,16 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8723,19 +8675,19 @@
         <v>78</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -8747,13 +8699,13 @@
         <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
@@ -8764,14 +8716,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8790,19 +8742,19 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L65" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O65" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -8851,7 +8803,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -8863,7 +8815,7 @@
         <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
@@ -8880,10 +8832,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8909,10 +8861,10 @@
         <v>108</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8939,13 +8891,13 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -8963,7 +8915,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>88</v>
@@ -8992,10 +8944,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9021,13 +8973,13 @@
         <v>102</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9077,7 +9029,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>88</v>
@@ -9106,10 +9058,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9132,17 +9084,15 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -9191,7 +9141,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9220,10 +9170,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9246,17 +9196,15 @@
         <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -9305,7 +9253,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9334,10 +9282,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9360,17 +9308,15 @@
         <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -9419,7 +9365,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9448,10 +9394,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9474,17 +9420,15 @@
         <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -9533,7 +9477,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -9562,10 +9506,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9588,13 +9532,13 @@
         <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9645,7 +9589,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -9654,7 +9598,7 @@
         <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>100</v>
@@ -9663,7 +9607,7 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -9674,10 +9618,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9700,13 +9644,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9757,7 +9701,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -9775,7 +9719,7 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -9786,14 +9730,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9812,16 +9756,16 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9859,19 +9803,19 @@
         <v>78</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -9883,13 +9827,13 @@
         <v>78</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -9900,14 +9844,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -9926,19 +9870,19 @@
         <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L75" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O75" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -9987,7 +9931,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -9999,7 +9943,7 @@
         <v>78</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>78</v>
@@ -10016,10 +9960,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10042,17 +9986,15 @@
         <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -10101,7 +10043,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>88</v>
@@ -10130,10 +10072,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10159,14 +10101,12 @@
         <v>102</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -10215,7 +10155,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10244,10 +10184,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10270,16 +10210,16 @@
         <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10329,7 +10269,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10358,10 +10298,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10384,16 +10324,16 @@
         <v>89</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10443,7 +10383,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -10472,10 +10412,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10498,16 +10438,16 @@
         <v>89</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10557,7 +10497,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -10575,7 +10515,7 @@
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>78</v>
@@ -10586,13 +10526,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>78</v>
@@ -10614,13 +10554,13 @@
         <v>89</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10671,7 +10611,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -10680,16 +10620,16 @@
         <v>80</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
@@ -10700,10 +10640,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10726,13 +10666,13 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10783,7 +10723,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -10801,7 +10741,7 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
@@ -10812,14 +10752,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -10838,16 +10778,16 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -10885,19 +10825,19 @@
         <v>78</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -10909,13 +10849,13 @@
         <v>78</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -10926,14 +10866,14 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -10952,19 +10892,19 @@
         <v>89</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L84" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O84" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -11013,7 +10953,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11025,7 +10965,7 @@
         <v>78</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>78</v>
@@ -11042,10 +10982,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11071,10 +11011,10 @@
         <v>81</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11125,7 +11065,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11137,7 +11077,7 @@
         <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>78</v>
@@ -11154,10 +11094,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11183,13 +11123,13 @@
         <v>102</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11239,7 +11179,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -11268,10 +11208,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11294,16 +11234,16 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11353,7 +11293,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -11371,7 +11311,7 @@
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
@@ -11382,10 +11322,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11408,13 +11348,13 @@
         <v>89</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11465,7 +11405,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -11474,7 +11414,7 @@
         <v>88</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>100</v>
@@ -11483,7 +11423,7 @@
         <v>78</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
@@ -11494,10 +11434,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11520,13 +11460,13 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -11577,7 +11517,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -11595,7 +11535,7 @@
         <v>78</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
@@ -11606,14 +11546,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -11632,16 +11572,16 @@
         <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11679,19 +11619,19 @@
         <v>78</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -11703,13 +11643,13 @@
         <v>78</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -11720,14 +11660,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -11746,19 +11686,19 @@
         <v>89</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L91" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O91" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -11807,7 +11747,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -11819,7 +11759,7 @@
         <v>78</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>78</v>
@@ -11836,10 +11776,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11865,13 +11805,13 @@
         <v>108</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11897,13 +11837,13 @@
         <v>78</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
@@ -11921,7 +11861,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -11950,10 +11890,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11976,16 +11916,16 @@
         <v>89</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12035,7 +11975,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12064,10 +12004,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12090,13 +12030,13 @@
         <v>89</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12147,7 +12087,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -12156,7 +12096,7 @@
         <v>88</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>100</v>
@@ -12165,7 +12105,7 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>78</v>
@@ -12176,10 +12116,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12202,13 +12142,13 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12259,7 +12199,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -12277,7 +12217,7 @@
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
@@ -12288,14 +12228,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12314,16 +12254,16 @@
         <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12361,19 +12301,19 @@
         <v>78</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -12385,13 +12325,13 @@
         <v>78</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -12402,14 +12342,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -12428,19 +12368,19 @@
         <v>89</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L97" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O97" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>78</v>
@@ -12489,7 +12429,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -12501,7 +12441,7 @@
         <v>78</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>78</v>
@@ -12518,10 +12458,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12547,10 +12487,10 @@
         <v>108</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -12577,13 +12517,13 @@
         <v>78</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>78</v>
@@ -12601,7 +12541,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>88</v>
@@ -12630,10 +12570,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12659,13 +12599,13 @@
         <v>102</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12715,7 +12655,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>88</v>
@@ -12744,10 +12684,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12770,17 +12710,15 @@
         <v>89</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -12829,7 +12767,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -12858,10 +12796,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12884,17 +12822,15 @@
         <v>89</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -12943,7 +12879,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -12972,10 +12908,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12998,17 +12934,15 @@
         <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -13057,7 +12991,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -13086,10 +13020,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13112,17 +13046,15 @@
         <v>89</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -13171,7 +13103,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -13200,10 +13132,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13226,13 +13158,13 @@
         <v>89</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -13283,7 +13215,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -13292,7 +13224,7 @@
         <v>88</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>100</v>
@@ -13301,7 +13233,7 @@
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -13312,10 +13244,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13338,13 +13270,13 @@
         <v>78</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13395,7 +13327,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -13413,7 +13345,7 @@
         <v>78</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -13424,14 +13356,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -13450,16 +13382,16 @@
         <v>78</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N106" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -13497,19 +13429,19 @@
         <v>78</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -13521,13 +13453,13 @@
         <v>78</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
@@ -13538,14 +13470,14 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -13564,19 +13496,19 @@
         <v>89</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L107" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O107" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>78</v>
@@ -13625,7 +13557,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -13637,7 +13569,7 @@
         <v>78</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>78</v>
@@ -13654,10 +13586,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13680,17 +13612,15 @@
         <v>89</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -13739,7 +13669,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>88</v>
@@ -13768,10 +13698,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13797,14 +13727,12 @@
         <v>102</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>78</v>
@@ -13853,7 +13781,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -13882,10 +13810,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13908,16 +13836,16 @@
         <v>89</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -13967,7 +13895,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -13996,10 +13924,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14022,16 +13950,16 @@
         <v>89</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14081,7 +14009,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -14110,10 +14038,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14136,16 +14064,16 @@
         <v>89</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14195,7 +14123,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -14213,7 +14141,7 @@
         <v>78</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
@@ -14224,10 +14152,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14250,19 +14178,19 @@
         <v>89</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>78</v>
@@ -14311,7 +14239,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -14320,7 +14248,7 @@
         <v>88</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>100</v>
@@ -14329,7 +14257,7 @@
         <v>78</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
